--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N18_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.7800257980555</v>
+        <v>2.88925419218402</v>
       </c>
       <c r="D2" t="n">
-        <v>13.93714968653857</v>
+        <v>2.264786824062518</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
